--- a/data/env_test/case_excle/CompanyPurcharsZX/case_data_zz.xlsx
+++ b/data/env_test/case_excle/CompanyPurcharsZX/case_data_zz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/CompanyPurcharsZX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726BA34A-E394-B341-917F-212F8230957C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18CF029-F3E9-6E4E-A449-1CA7E4B5EAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="500" windowWidth="51200" windowHeight="27040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="500" windowWidth="51200" windowHeight="27040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公开" sheetId="10" r:id="rId1"/>
@@ -572,11 +572,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"1887306232988766210\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>P2</t>
+  </si>
+  <si>
+    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"${catalogId}\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1304,7 +1304,7 @@
         <v>52</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>16</v>
@@ -1336,7 +1336,7 @@
         <v>48</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1365,7 +1365,7 @@
         <v>60</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -1397,7 +1397,7 @@
         <v>56</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>16</v>
@@ -1430,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>16</v>
@@ -1461,7 +1461,7 @@
         <v>115</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -1495,7 +1495,7 @@
         <v>73</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>16</v>
@@ -1524,7 +1524,7 @@
         <v>79</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -1559,7 +1559,7 @@
         <v>80</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>16</v>
@@ -1588,7 +1588,7 @@
         <v>34</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>16</v>
@@ -1617,7 +1617,7 @@
         <v>85</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>16</v>
@@ -1646,7 +1646,7 @@
         <v>91</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>22</v>
@@ -1675,7 +1675,7 @@
         <v>97</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>22</v>
@@ -1704,7 +1704,7 @@
         <v>92</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
@@ -1733,7 +1733,7 @@
         <v>93</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>22</v>
@@ -1762,7 +1762,7 @@
         <v>48</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>23</v>
@@ -1791,7 +1791,7 @@
         <v>104</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>16</v>
@@ -1820,7 +1820,7 @@
         <v>110</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
@@ -1855,7 +1855,7 @@
         <v>48</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>23</v>
@@ -1887,7 +1887,7 @@
         <v>107</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>16</v>
@@ -1905,19 +1905,19 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2809,19 +2809,19 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3015,7 +3015,7 @@
         <v>52</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>16</v>
@@ -3047,7 +3047,7 @@
         <v>48</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -3076,7 +3076,7 @@
         <v>60</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -3108,7 +3108,7 @@
         <v>56</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>16</v>
@@ -3141,7 +3141,7 @@
         <v>74</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>16</v>
@@ -3172,7 +3172,7 @@
         <v>115</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -3206,16 +3206,16 @@
         <v>73</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>21</v>
@@ -3235,7 +3235,7 @@
         <v>79</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -3270,7 +3270,7 @@
         <v>80</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>16</v>
@@ -3299,7 +3299,7 @@
         <v>34</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>16</v>
@@ -3328,7 +3328,7 @@
         <v>85</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>16</v>
@@ -3357,7 +3357,7 @@
         <v>91</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>22</v>
@@ -3386,7 +3386,7 @@
         <v>97</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>22</v>
@@ -3415,7 +3415,7 @@
         <v>92</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
@@ -3444,7 +3444,7 @@
         <v>93</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>22</v>
@@ -3473,7 +3473,7 @@
         <v>48</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>23</v>
@@ -3502,7 +3502,7 @@
         <v>104</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>16</v>
@@ -3531,7 +3531,7 @@
         <v>110</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
@@ -3566,7 +3566,7 @@
         <v>48</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>23</v>
@@ -3598,7 +3598,7 @@
         <v>107</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>16</v>
@@ -3616,19 +3616,19 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
